--- a/output/补测名单_2024-2025-1_初一.xlsx
+++ b/output/补测名单_2024-2025-1_初一.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,17 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>需补测项目数</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>需补测项目</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>补测原因</t>
         </is>
       </c>
     </row>
@@ -490,9 +500,17 @@
           <t>不及格</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>身高体重指数(BMI), 50米跑, 坐位体前屈, 1000米跑(男)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分)), 坐位体前屈(不及格(50分)), 1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -502,17 +520,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C2024003</t>
+          <t>C2024001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>学生003</t>
+          <t>学生001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -521,16 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>67.5</v>
+        <v>69</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 坐位体前屈</t>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>立定跳远, 引体向上(男), 1000米跑(男)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>立定跳远(不及格(50分)), 引体向上(男)(不及格(50分)), 1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -540,17 +566,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C2024001</t>
+          <t>C2024010</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>学生001</t>
+          <t>学生010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -559,16 +585,24 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>74.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>立定跳远, 引体向上(男), 1000米跑(男)</t>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 坐位体前屈, 800米跑(女)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分)), 800米跑(女)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -578,17 +612,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C2024013</t>
+          <t>C2024003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>学生013</t>
+          <t>学生003</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -597,16 +631,24 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>67.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 50米跑</t>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -616,17 +658,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C2024012</t>
+          <t>C2024008</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>学生012</t>
+          <t>学生008</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -635,16 +677,24 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>81.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>及格</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1000米跑(男)</t>
+          <t>良好</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 仰卧起坐(女)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -654,12 +704,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C2024010</t>
+          <t>C2024011</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>学生010</t>
+          <t>学生011</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -673,16 +723,24 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 坐位体前屈, 800米跑(女)</t>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50米跑, 仰卧起坐(女)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>50米跑(缺考), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -692,17 +750,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C2024005</t>
+          <t>C2024013</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>学生005</t>
+          <t>学生013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -711,16 +769,24 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>坐位体前屈</t>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 50米跑</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -756,9 +822,17 @@
           <t>及格</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>身高体重指数(BMI), 50米跑</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -794,9 +868,17 @@
           <t>及格</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>立定跳远</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>立定跳远(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -806,12 +888,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C2024011</t>
+          <t>C2024005</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>学生011</t>
+          <t>学生005</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -825,16 +907,24 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>78.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>仰卧起坐(女)</t>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>坐位体前屈(不及格(30分))</t>
         </is>
       </c>
     </row>
@@ -863,16 +953,24 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>78.8</v>
+        <v>77.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -882,17 +980,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C2024008</t>
+          <t>C2024009</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>学生008</t>
+          <t>学生009</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -901,16 +999,24 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>81.5</v>
+        <v>89.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 仰卧起坐(女)</t>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>肺活量</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>肺活量(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -920,12 +1026,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C2024009</t>
+          <t>C2024012</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>学生009</t>
+          <t>学生012</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -939,16 +1045,24 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>89.5</v>
+        <v>71</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>良好</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>肺活量</t>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1000米跑(男)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -984,9 +1098,17 @@
           <t>不及格</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>50米跑, 立定跳远, 坐位体前屈, 引体向上(男)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>50米跑(不及格(50分)), 立定跳远(不及格(50分)), 坐位体前屈(不及格(50分)), 引体向上(男)(不及格(30分))</t>
         </is>
       </c>
     </row>
@@ -996,12 +1118,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C2024028</t>
+          <t>C2024027</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>学生028</t>
+          <t>学生027</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1015,16 +1137,24 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>64.5</v>
+        <v>74.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>肺活量, 50米跑, 引体向上(男)</t>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 坐位体前屈, 引体向上(男)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分)), 引体向上(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1164,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C2024016</t>
+          <t>C2024028</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>学生016</t>
+          <t>学生028</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1053,16 +1183,24 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>74.5</v>
+        <v>64.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>引体向上(男)</t>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>肺活量, 50米跑, 引体向上(男)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>肺活量(不及格(50分)), 50米跑(不及格(50分)), 引体向上(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1210,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C2024018</t>
+          <t>C2024017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>学生018</t>
+          <t>学生017</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1091,16 +1229,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>74.5</v>
+        <v>76.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>800米跑(女)</t>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 50米跑</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1256,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C2024027</t>
+          <t>C2024024</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>学生027</t>
+          <t>学生024</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1129,16 +1275,24 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>74.5</v>
+        <v>82.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>及格</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 坐位体前屈, 引体向上(男)</t>
+          <t>良好</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 引体向上(男)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 引体向上(男)(不及格(30分))</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1302,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C2024017</t>
+          <t>C2024026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>学生017</t>
+          <t>学生026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1167,16 +1321,24 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>76.5</v>
+        <v>78.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 50米跑</t>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1212,9 +1374,17 @@
           <t>及格</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>身高体重指数(BMI), 仰卧起坐(女)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1394,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C2024026</t>
+          <t>C2024016</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>学生026</t>
+          <t>学生016</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1243,16 +1413,24 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>78.5</v>
+        <v>74.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 坐位体前屈</t>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>引体向上(男)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>引体向上(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1440,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C2024020</t>
+          <t>C2024018</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>学生020</t>
+          <t>学生018</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1281,16 +1459,24 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>80</v>
+        <v>74.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>良好</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI)</t>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>800米跑(女)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>800米跑(女)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1486,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C2024029</t>
+          <t>C2024019</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>学生029</t>
+          <t>学生019</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1319,16 +1505,24 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>50米跑</t>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1532,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C2024023</t>
+          <t>C2024020</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>学生023</t>
+          <t>学生020</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1357,16 +1551,24 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>81.5</v>
+        <v>80</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>坐位体前屈</t>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1578,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C2024022</t>
+          <t>C2024001</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>学生022</t>
+          <t>学生021</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1395,16 +1597,24 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>坐位体前屈</t>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1624,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C2024001</t>
+          <t>C2024022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>学生021</t>
+          <t>学生022</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1433,16 +1643,24 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>82.5</v>
+        <v>82</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI)</t>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1670,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C2024024</t>
+          <t>C2024023</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>学生024</t>
+          <t>学生023</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1471,16 +1689,24 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>82.5</v>
+        <v>81.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 引体向上(男)</t>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1716,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C2024019</t>
+          <t>C2024029</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>学生019</t>
+          <t>学生029</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1509,16 +1735,24 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>坐位体前屈</t>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50米跑</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>50米跑(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1762,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C2024037</t>
+          <t>C2024043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>学生037</t>
+          <t>学生043</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1547,16 +1781,24 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>61</v>
+        <v>73.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 1000米跑(男)</t>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 坐位体前屈, 仰卧起坐(女)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分)), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1808,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C2024032</t>
+          <t>C2024036</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>学生032</t>
+          <t>学生036</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1585,16 +1827,24 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>65.5</v>
+        <v>67.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1000米跑(男)</t>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1854,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C2024036</t>
+          <t>C2024037</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>学生036</t>
+          <t>学生037</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1623,16 +1873,24 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>67.5</v>
+        <v>61</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 坐位体前屈</t>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 1000米跑(男)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 1000米跑(男)(不及格(30分))</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1900,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C2024040</t>
+          <t>C2024038</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>学生040</t>
+          <t>学生038</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1661,16 +1919,24 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>71.5</v>
+        <v>73</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 坐位体前屈</t>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50米跑, 引体向上(男)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>50米跑(不及格(50分)), 引体向上(男)(不及格(30分))</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1946,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C2024042</t>
+          <t>C2024040</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>学生042</t>
+          <t>学生040</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1699,16 +1965,24 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>50米跑, 坐位体前屈</t>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI), 坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1992,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C2024038</t>
+          <t>C2024042</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>学生038</t>
+          <t>学生042</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1737,16 +2011,24 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>50米跑, 引体向上(男)</t>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50米跑, 坐位体前屈</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>50米跑(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1756,17 +2038,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C2024043</t>
+          <t>C2024032</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>学生043</t>
+          <t>学生032</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1775,16 +2057,24 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>73.5</v>
+        <v>65.5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>及格</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI), 坐位体前屈, 仰卧起坐(女)</t>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1000米跑(男)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1794,12 +2084,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C2024044</t>
+          <t>C2024033</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>学生044</t>
+          <t>学生033</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1813,16 +2103,24 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>74.5</v>
+        <v>85.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>及格</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1000米跑(男)</t>
+          <t>良好</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1832,12 +2130,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C2024041</t>
+          <t>C2024034</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>学生041</t>
+          <t>学生034</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1851,16 +2149,24 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>80.5</v>
+        <v>88.5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI)</t>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>仰卧起坐(女)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1870,17 +2176,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C2024033</t>
+          <t>C2024041</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>学生033</t>
+          <t>学生041</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1889,16 +2195,24 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>85.5</v>
+        <v>80.5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>身高体重指数(BMI)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1908,17 +2222,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C2024045</t>
+          <t>C2024044</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>学生045</t>
+          <t>学生044</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1927,16 +2241,24 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>85.5</v>
+        <v>74.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>良好</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>身高体重指数(BMI)</t>
+          <t>及格</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1000米跑(男)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
     </row>
@@ -1946,12 +2268,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C2024034</t>
+          <t>C2024045</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>学生034</t>
+          <t>学生045</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1965,16 +2287,24 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>88.5</v>
+        <v>85.5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>仰卧起坐(女)</t>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
     </row>

--- a/output/补测名单_2024-2025-1_初一.xlsx
+++ b/output/补测名单_2024-2025-1_初一.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>补测原因</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>原因分类</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -513,6 +518,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分)), 坐位体前屈(不及格(50分)), 1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -559,6 +569,11 @@
           <t>立定跳远(不及格(50分)), 引体向上(男)(不及格(50分)), 1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -605,6 +620,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分)), 800米跑(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -651,6 +671,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -697,6 +722,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -743,6 +773,11 @@
           <t>50米跑(缺考), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>部分缺项</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -789,6 +824,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -835,6 +875,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -881,6 +926,11 @@
           <t>立定跳远(不及格(50分))</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -927,6 +977,11 @@
           <t>坐位体前屈(不及格(30分))</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -973,6 +1028,11 @@
           <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1019,6 +1079,11 @@
           <t>肺活量(不及格(50分))</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1065,6 +1130,11 @@
           <t>1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1111,6 +1181,11 @@
           <t>50米跑(不及格(50分)), 立定跳远(不及格(50分)), 坐位体前屈(不及格(50分)), 引体向上(男)(不及格(30分))</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1157,6 +1232,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分)), 引体向上(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1203,6 +1283,11 @@
           <t>肺活量(不及格(50分)), 50米跑(不及格(50分)), 引体向上(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1249,6 +1334,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1295,6 +1385,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 引体向上(男)(不及格(30分))</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1341,6 +1436,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1387,6 +1487,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1433,6 +1538,11 @@
           <t>引体向上(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1479,6 +1589,11 @@
           <t>800米跑(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1525,6 +1640,11 @@
           <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1571,6 +1691,11 @@
           <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1617,6 +1742,11 @@
           <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1663,6 +1793,11 @@
           <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1709,6 +1844,11 @@
           <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1755,6 +1895,11 @@
           <t>50米跑(不及格(50分))</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1801,6 +1946,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分)), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1847,6 +1997,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1893,6 +2048,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 1000米跑(男)(不及格(30分))</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1939,6 +2099,11 @@
           <t>50米跑(不及格(50分)), 引体向上(男)(不及格(30分))</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1985,6 +2150,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2031,6 +2201,11 @@
           <t>50米跑(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2077,6 +2252,11 @@
           <t>1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2123,6 +2303,11 @@
           <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2169,6 +2354,11 @@
           <t>仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2215,6 +2405,11 @@
           <t>身高体重指数(BMI)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2261,6 +2456,11 @@
           <t>1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2305,6 +2505,11 @@
       <c r="J41" t="inlineStr">
         <is>
           <t>身高体重指数(BMI)(不及格(50分))</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
         </is>
       </c>
     </row>
